--- a/diseases/d178/2010-2014.xlsx
+++ b/diseases/d178/2010-2014.xlsx
@@ -869,12 +869,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -908,84 +908,95 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00861176274645304</v>
+        <v>0.1374393645669358</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1023,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1047,93 +1058,179 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2010-02-01</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2010-02</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.01652022779669833</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1195,25 +1292,25 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2010-02-01</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2010-02</t>
+          <t>2010-01</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01291764411967956</v>
+        <v>0.00861176274645304</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1343,25 +1440,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2010-03-01</t>
+          <t>2010-02-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2010-03</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="O6" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0340729698306903</v>
+        <v>0.01652022779669833</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1491,25 +1588,25 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2010-03-01</t>
+          <t>2010-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2010-03</t>
+          <t>2010-02</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03014116961258564</v>
+        <v>0.01291764411967956</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1639,25 +1736,25 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2010-04-01</t>
+          <t>2010-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2010-04</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.02426408457640067</v>
+        <v>0.0340729698306903</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1787,25 +1884,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2010-04-01</t>
+          <t>2010-03-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2010-04</t>
+          <t>2010-03</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02583528823935912</v>
+        <v>0.03014116961258564</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1935,25 +2032,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2010-05-01</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2010-05</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="O10" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02736162728828161</v>
+        <v>0.02426408457640067</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2083,25 +2180,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2010-05-01</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2010-05</t>
+          <t>2010-04</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0215294068661326</v>
+        <v>0.02583528823935912</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2231,25 +2328,25 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2010-06-01</t>
+          <t>2010-05-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2010-06</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02839414152557525</v>
+        <v>0.02736162728828161</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2379,25 +2476,25 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2010-06-01</t>
+          <t>2010-05-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2010-06</t>
+          <t>2010-05</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03875293235903868</v>
+        <v>0.0215294068661326</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2527,25 +2624,25 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2010-07</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02374782745775385</v>
+        <v>0.02839414152557525</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2675,25 +2772,25 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2010-07</t>
+          <t>2010-06</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.00861176274645304</v>
+        <v>0.03875293235903868</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2823,25 +2920,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2010-08-01</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2010-08</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="O16" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.03200794135610301</v>
+        <v>0.02374782745775385</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2971,25 +3068,25 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2010-08-01</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2010-08</t>
+          <t>2010-07</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.00430588137322652</v>
+        <v>0.00861176274645304</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3119,25 +3216,25 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2010-09-01</t>
+          <t>2010-08-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2010-09</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="O18" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.02426408457640067</v>
+        <v>0.03200794135610301</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3267,25 +3364,25 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2010-09-01</t>
+          <t>2010-08-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2010-09</t>
+          <t>2010-08</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.01722352549290608</v>
+        <v>0.00430588137322652</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3415,25 +3512,25 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2010-10-01</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2010-10</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O20" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.02168279898316656</v>
+        <v>0.02426408457640067</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3563,25 +3660,25 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2010-10-01</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2010-10</t>
+          <t>2010-09</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.03014116961258564</v>
+        <v>0.01722352549290608</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3711,25 +3808,25 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2010-11-01</t>
+          <t>2010-10-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2010-11</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="O22" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.01652022779669833</v>
+        <v>0.02168279898316656</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3859,25 +3956,25 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2010-11-01</t>
+          <t>2010-10-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2010-11</t>
+          <t>2010-10</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.01722352549290608</v>
+        <v>0.03014116961258564</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -4007,25 +4104,25 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.01961777050857927</v>
+        <v>0.01652022779669833</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4155,25 +4252,25 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2010-12-01</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2010-12</t>
+          <t>2010-11</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01291764411967956</v>
+        <v>0.01722352549290608</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4303,25 +4400,25 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2010-12-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O26" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02253120302140155</v>
+        <v>0.01961777050857927</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4451,25 +4548,25 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2011-01-01</t>
+          <t>2010-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2011-01</t>
+          <t>2010-12</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01718724209066214</v>
+        <v>0.01291764411967956</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4599,25 +4696,25 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O28" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02048291183763777</v>
+        <v>0.02253120302140155</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -4717,12 +4814,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4747,93 +4844,104 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2011-02</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01718724209066214</v>
+        <v>0.1273315694534748</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4860,17 +4968,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4895,93 +5003,179 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2011-03-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="O30" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.0322605861442795</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN30" t="b">
+        <v>1</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5043,25 +5237,25 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2011-03-01</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2011-03</t>
+          <t>2011-01</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.01289043156799661</v>
+        <v>0.01718724209066214</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5191,25 +5385,25 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2011-04-01</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O32" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.02457949420516533</v>
+        <v>0.02048291183763777</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -5339,12 +5533,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2011-04-01</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2011-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5487,25 +5681,25 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2011-05-01</t>
+          <t>2011-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="O34" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.018434620653874</v>
+        <v>0.0322605861442795</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5635,12 +5829,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2011-05-01</t>
+          <t>2011-03-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2011-03</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5783,25 +5977,25 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2011-04-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="O36" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>0.0322605861442795</v>
+        <v>0.02457949420516533</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -5931,25 +6125,25 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2011-04-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2011-04</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01289043156799661</v>
+        <v>0.01718724209066214</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6079,25 +6273,25 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2011-07-01</t>
+          <t>2011-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="O38" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.02970022216457477</v>
+        <v>0.018434620653874</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6227,25 +6421,25 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2011-07-01</t>
+          <t>2011-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2011-05</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0.004296810522665536</v>
+        <v>0.01289043156799661</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6375,25 +6569,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2011-08-01</t>
+          <t>2011-06-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="O40" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.02457949420516533</v>
+        <v>0.0322605861442795</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6523,25 +6717,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2011-08-01</t>
+          <t>2011-06-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2011-06</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.008593621045331071</v>
+        <v>0.01289043156799661</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6671,25 +6865,25 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2011-07-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="O42" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.03379680453210233</v>
+        <v>0.02970022216457477</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -6819,25 +7013,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2011-09-01</t>
+          <t>2011-07-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2011-09</t>
+          <t>2011-07</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.03007767365865875</v>
+        <v>0.004296810522665536</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -6967,25 +7161,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2011-10-01</t>
+          <t>2011-08-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O44" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.01997083904169683</v>
+        <v>0.02457949420516533</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7115,12 +7309,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2011-10-01</t>
+          <t>2011-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2011-08</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7263,25 +7457,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="O46" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.02201913022546061</v>
+        <v>0.03379680453210233</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7411,25 +7605,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2011-09</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.03437448418132429</v>
+        <v>0.03007767365865875</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7559,25 +7753,25 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-10-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="O48" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.027651930980811</v>
+        <v>0.01997083904169683</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7707,25 +7901,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2011-12-01</t>
+          <t>2011-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2011-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.02578086313599321</v>
+        <v>0.008593621045331071</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -7855,25 +8049,25 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.02285701381297344</v>
+        <v>0.02201913022546061</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8003,25 +8197,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2011-11</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.02998377321027821</v>
+        <v>0.03437448418132429</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8151,25 +8345,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2012-02-01</t>
+          <t>2011-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2011-12</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="O52" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.02387288109355004</v>
+        <v>0.027651930980811</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8299,25 +8493,25 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2012-02-01</t>
+          <t>2011-12-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2011-12</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.004283396172896888</v>
+        <v>0.02578086313599321</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8447,25 +8641,25 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2012-03-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="O54" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.02742841657556814</v>
+        <v>0.02285701381297344</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8565,12 +8759,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8595,93 +8789,104 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2012-03-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R55" t="n">
-        <v>0.04283396172896888</v>
+        <v>0.09449490981692156</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8913,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8743,93 +8948,179 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2012-04-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="O56" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.02336494745326174</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8891,25 +9182,25 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2012-04-01</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2012-01</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01713358469158755</v>
+        <v>0.02998377321027821</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -9039,25 +9330,25 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2012-05-01</t>
+          <t>2012-02-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2012-02</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="O58" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.02946015113672133</v>
+        <v>0.02387288109355004</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9187,25 +9478,25 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2012-05-01</t>
+          <t>2012-02-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2012-02</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.05568415024765953</v>
+        <v>0.004283396172896888</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -9335,25 +9626,25 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2012-06-01</t>
+          <t>2012-03-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2012-03</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O60" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.02285701381297344</v>
+        <v>0.02742841657556814</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9483,25 +9774,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2012-06-01</t>
+          <t>2012-03-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2012-03</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.03855056555607199</v>
+        <v>0.04283396172896888</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9631,25 +9922,25 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2012-07-01</t>
+          <t>2012-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2012-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="O62" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.01930147833095535</v>
+        <v>0.02336494745326174</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -9779,25 +10070,25 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2012-07-01</t>
+          <t>2012-04-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2012-04</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0342671693831751</v>
+        <v>0.01713358469158755</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -9927,25 +10218,25 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2012-08-01</t>
+          <t>2012-05-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2012-05</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="O64" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03149188569787453</v>
+        <v>0.02946015113672133</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10075,25 +10366,25 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2012-08-01</t>
+          <t>2012-05-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2012-05</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.008566792345793776</v>
+        <v>0.05568415024765953</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10223,25 +10514,25 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2012-09-01</t>
+          <t>2012-06-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-06</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O66" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.02184114653239685</v>
+        <v>0.02285701381297344</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10371,25 +10662,25 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2012-09-01</t>
+          <t>2012-06-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2012-06</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.008566792345793776</v>
+        <v>0.03855056555607199</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -10519,25 +10810,25 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2012-10-01</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2012-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="O68" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>0.02844428385614473</v>
+        <v>0.01930147833095535</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -10637,12 +10928,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10667,25 +10958,25 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2012-11-01</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2012-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01879354469066705</v>
+        <v>0.0342671693831751</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -10718,42 +11009,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10785,12 +11076,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10815,25 +11106,25 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2012-11-01</t>
+          <t>2012-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2012-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.008566792345793776</v>
+        <v>0.03149188569787453</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -10866,42 +11157,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -10933,12 +11224,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10963,25 +11254,25 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.01117454008634257</v>
+        <v>0.008566792345793776</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -11014,42 +11305,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11081,12 +11372,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11111,25 +11402,25 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2012-12-01</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.004283396172896888</v>
+        <v>0.02184114653239685</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -11162,42 +11453,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -11229,12 +11520,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11259,25 +11550,25 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-09</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.01864183645930521</v>
+        <v>0.008566792345793776</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -11310,42 +11601,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11377,12 +11668,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11407,25 +11698,25 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2013-01-01</t>
+          <t>2012-10-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2012-10</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.01281127419459843</v>
+        <v>0.02844428385614473</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -11458,42 +11749,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -11555,25 +11846,25 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2013-02-01</t>
+          <t>2012-11-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O75" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.0176341696236671</v>
+        <v>0.01879354469066705</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -11703,12 +11994,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2013-02-01</t>
+          <t>2012-11-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2012-11</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11721,7 +12012,7 @@
         <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>0.00854084946306562</v>
+        <v>0.008566792345793776</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -11851,25 +12142,25 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2013-03-01</t>
+          <t>2012-12-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="O77" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0201533367127624</v>
+        <v>0.01117454008634257</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -11999,25 +12290,25 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2013-03-01</t>
+          <t>2012-12-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2012-12</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01281127419459843</v>
+        <v>0.004283396172896888</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -12147,25 +12438,25 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2013-04-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="O79" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.02619933772659111</v>
+        <v>0.01864183645930521</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -12265,12 +12556,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12295,93 +12586,104 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2013-04-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="O80" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01281127419459843</v>
+        <v>0.102001980113439</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12408,17 +12710,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12443,93 +12745,179 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2013-05-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="O81" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.02569550430877205</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -12591,25 +12979,25 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2013-05-01</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2013-01</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.00854084946306562</v>
+        <v>0.01281127419459843</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -12739,25 +13127,25 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O83" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.02468783747313394</v>
+        <v>0.0176341696236671</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -12887,25 +13275,25 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2013-02</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.02135212365766405</v>
+        <v>0.00854084946306562</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -13035,25 +13423,25 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2013-07-01</t>
+          <t>2013-03-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O85" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.02065717013058145</v>
+        <v>0.0201533367127624</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -13153,12 +13541,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -13183,25 +13571,25 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2013-03-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-03</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.01713033620584804</v>
+        <v>0.01281127419459843</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -13234,42 +13622,42 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13301,12 +13689,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13331,25 +13719,25 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2013-04-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.00427042473153281</v>
+        <v>0.02619933772659111</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -13382,42 +13770,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -13449,12 +13837,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13479,25 +13867,25 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2013-04-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-04</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.01612266937020992</v>
+        <v>0.01281127419459843</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -13530,42 +13918,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13597,12 +13985,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13627,25 +14015,25 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2013-05-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.00427042473153281</v>
+        <v>0.02569550430877205</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -13678,42 +14066,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -13745,12 +14133,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13775,25 +14163,25 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
+          <t>2013-05-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2013-05</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01309966886329556</v>
+        <v>0.00854084946306562</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -13826,42 +14214,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13923,25 +14311,25 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2013-11-01</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="O91" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.0201533367127624</v>
+        <v>0.02468783747313394</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -14071,25 +14459,25 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2013-11-01</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2013-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01708169892613124</v>
+        <v>0.02135212365766405</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -14219,25 +14607,25 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-07</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="O93" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.01612266937020992</v>
+        <v>0.02065717013058145</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -14337,12 +14725,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14367,25 +14755,25 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2013-12-01</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="O94" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01281127419459843</v>
+        <v>0.01713033620584804</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -14418,42 +14806,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -14485,12 +14873,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14515,25 +14903,25 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-08</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.02798808729046612</v>
+        <v>0.00427042473153281</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -14566,42 +14954,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14633,12 +15021,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14663,25 +15051,25 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2014-01-01</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.01278074204604897</v>
+        <v>0.01612266937020992</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -14714,42 +15102,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -14781,12 +15169,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14811,25 +15199,25 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2014-02-01</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-09</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.02099106546784959</v>
+        <v>0.00427042473153281</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -14862,42 +15250,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14929,12 +15317,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14959,25 +15347,25 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2014-02-01</t>
+          <t>2013-10-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2013-10</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.00426024734868299</v>
+        <v>0.01309966886329556</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -15010,42 +15398,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -15107,25 +15495,25 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2013-11-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O99" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.01899191637567344</v>
+        <v>0.0201533367127624</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -15255,12 +15643,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2014-03-01</t>
+          <t>2013-11-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2013-11</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15273,7 +15661,7 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01704098939473196</v>
+        <v>0.01708169892613124</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -15403,25 +15791,25 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2014-04-01</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="O101" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0184921291026294</v>
+        <v>0.01612266937020992</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -15551,25 +15939,25 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2014-04-01</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2013-12</t>
         </is>
       </c>
       <c r="N102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.008520494697365981</v>
+        <v>0.01281127419459843</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -15699,25 +16087,25 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2014-05-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O103" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0.02648872547133401</v>
+        <v>0.02798808729046612</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -15817,12 +16205,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15847,93 +16235,104 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="O104" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="R104" t="n">
-        <v>0.01799234182958536</v>
+        <v>0.1431206793427904</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15960,17 +16359,17 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15995,93 +16394,179 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="O105" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.03408197878946392</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Acute Flaccid Paralysis</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D177_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16113,12 +16598,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -16143,25 +16628,25 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-01</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="O106" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>0.02448957637915786</v>
+        <v>0.01278074204604897</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -16194,42 +16679,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16261,12 +16746,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16291,25 +16776,25 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2014-02-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="O107" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>0.0426024734868299</v>
+        <v>0.02099106546784959</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -16342,42 +16827,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -16409,12 +16894,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16439,25 +16924,25 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-02-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-02</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.0249893636522019</v>
+        <v>0.00426024734868299</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -16490,42 +16975,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16557,12 +17042,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -16587,25 +17072,25 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="O109" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>0.008520494697365981</v>
+        <v>0.01899191637567344</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -16638,42 +17123,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -16705,12 +17190,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16735,25 +17220,25 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-03</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="O110" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.02948744910959824</v>
+        <v>0.01704098939473196</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -16786,42 +17271,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16853,12 +17338,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16883,25 +17368,25 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0.00426024734868299</v>
+        <v>0.0184921291026294</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -16934,42 +17419,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -17001,12 +17486,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17031,25 +17516,25 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2014-10-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N112" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="O112" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>0.01649298001045325</v>
+        <v>0.008520494697365981</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -17082,42 +17567,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17179,25 +17664,25 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-05-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-05</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="O113" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>0.02149085274089363</v>
+        <v>0.02648872547133401</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -17297,12 +17782,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17327,25 +17812,25 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.00426024734868299</v>
+        <v>0.01799234182958536</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -17378,42 +17863,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -17445,12 +17930,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17475,25 +17960,25 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O115" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.0144938309182771</v>
+        <v>0.03408197878946392</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -17526,42 +18011,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17593,12 +18078,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17623,25 +18108,25 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-07-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-07</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.00426024734868299</v>
+        <v>0.02448957637915786</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -17674,40 +18159,1520 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>10</v>
+      </c>
+      <c r="O117" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.0426024734868299</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW116" t="inlineStr">
+      <c r="AW117" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
+      <c r="AX117" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY116" t="inlineStr">
+      <c r="AY117" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
+      <c r="AZ117" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA116" t="inlineStr">
+      <c r="BA117" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB116" t="inlineStr">
+      <c r="BB117" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC116" t="inlineStr">
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>50</v>
+      </c>
+      <c r="O118" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.0249893636522019</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.008520494697365981</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>59</v>
+      </c>
+      <c r="O120" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.02948744910959824</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.00426024734868299</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>33</v>
+      </c>
+      <c r="O122" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.01649298001045325</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>43</v>
+      </c>
+      <c r="O123" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.02149085274089363</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.00426024734868299</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>29</v>
+      </c>
+      <c r="O125" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.0144938309182771</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>acute-flaccid-paralysis</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D178</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Acute flaccid paralysis</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>急性无力肢体麻痹</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.00426024734868299</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -17829,7 +19794,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -17839,7 +19804,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -17859,7 +19824,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -17869,7 +19834,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -17891,7 +19856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2933</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="16">
